--- a/bankole_sex_specific_splicing_2026/documentation/02_summarized_data_analysis_documentation_03amm.xlsx
+++ b/bankole_sex_specific_splicing_2026/documentation/02_summarized_data_analysis_documentation_03amm.xlsx
@@ -232,7 +232,7 @@
 Track the sampleID (sample+techRep) by changing to “source” column in the GTF to be the sampleID</t>
   </si>
   <si>
-    <t xml:space="preserve">See row 10</t>
+    <t xml:space="preserve">see row 22</t>
   </si>
   <si>
     <t xml:space="preserve">ALN/
@@ -1042,7 +1042,7 @@
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1055,7 +1055,7 @@
       <c r="A3" s="5"/>
       <c r="C3" s="5"/>
     </row>
-    <row r="4" customFormat="false" ht="132.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -1139,7 +1139,7 @@
       <c r="AMI9" s="4"/>
       <c r="AMJ9" s="4"/>
     </row>
-    <row r="10" s="1" customFormat="true" ht="184.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="1" customFormat="true" ht="179.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
         <v>11</v>
       </c>
@@ -1178,7 +1178,7 @@
       <c r="AMI13" s="4"/>
       <c r="AMJ13" s="4"/>
     </row>
-    <row r="14" s="1" customFormat="true" ht="106.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="1" customFormat="true" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
         <v>12</v>
       </c>
@@ -1202,7 +1202,7 @@
       <c r="AMI15" s="4"/>
       <c r="AMJ15" s="4"/>
     </row>
-    <row r="16" s="1" customFormat="true" ht="106.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="1" customFormat="true" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
         <v>14</v>
       </c>
@@ -1226,7 +1226,7 @@
       <c r="AMI17" s="4"/>
       <c r="AMJ17" s="4"/>
     </row>
-    <row r="18" s="1" customFormat="true" ht="27.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="C18" s="5"/>
       <c r="AME18" s="3"/>
@@ -1245,7 +1245,7 @@
       <c r="AMI19" s="4"/>
       <c r="AMJ19" s="4"/>
     </row>
-    <row r="20" s="1" customFormat="true" ht="119.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="1" customFormat="true" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
         <v>15</v>
       </c>
@@ -1289,7 +1289,7 @@
       <c r="AMI22" s="4"/>
       <c r="AMJ22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="9.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="4"/>
